--- a/r5-aist-trustworthyai-poc-pipeline/ValueSet-eu-ai-intervention-vs.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/ValueSet-eu-ai-intervention-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes representing the type of human oversight or intervention.</t>
+    <t>Codes representing the type of human oversight or intervention (HL-03.1).</t>
   </si>
   <si>
     <t>Purpose</t>
